--- a/reports/excel-reports_cache_report:VI.xlsx
+++ b/reports/excel-reports_cache_report:VI.xlsx
@@ -27,7 +27,7 @@
     <x:t>AND INCOME DEPOSITED WITH THE BUREAU OF TREASURY</x:t>
   </x:si>
   <x:si>
-    <x:t>FOR THE MONTH OF April 2026</x:t>
+    <x:t>FOR THE MONTH OF May 2026</x:t>
   </x:si>
   <x:si>
     <x:t>Department of Information and Communications Technology</x:t>

--- a/reports/excel-reports_cache_report:VI.xlsx
+++ b/reports/excel-reports_cache_report:VI.xlsx
@@ -27,7 +27,7 @@
     <x:t>AND INCOME DEPOSITED WITH THE BUREAU OF TREASURY</x:t>
   </x:si>
   <x:si>
-    <x:t>FOR THE MONTH OF May 2026</x:t>
+    <x:t>FOR THE MONTH OF June 2026</x:t>
   </x:si>
   <x:si>
     <x:t>Department of Information and Communications Technology</x:t>
